--- a/data/fixtures-fichiers/xlsx-ALLOW-planning.xlsx
+++ b/data/fixtures-fichiers/xlsx-ALLOW-planning.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Planning" sheetId="1" r:id="rId1"/>
+    <sheet name="Ressources" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,6 +408,9 @@
         <v>Activité</v>
       </c>
       <c r="C1" t="str">
+        <v>Service</v>
+      </c>
+      <c r="D1" t="str">
         <v>Statut</v>
       </c>
     </row>
@@ -415,9 +419,12 @@
         <v>S12</v>
       </c>
       <c r="B2" t="str">
-        <v>Formation agents</v>
+        <v>Formation des nouveaux agents</v>
       </c>
       <c r="C2" t="str">
+        <v>Ressources humaines</v>
+      </c>
+      <c r="D2" t="str">
         <v>Planifié</v>
       </c>
     </row>
@@ -426,15 +433,129 @@
         <v>S13</v>
       </c>
       <c r="B3" t="str">
-        <v>Revue procédures</v>
+        <v>Revue des procédures d'archivage</v>
       </c>
       <c r="C3" t="str">
+        <v>Affaires administratives</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Planifié</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>S14</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Atelier sécurité informatique</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Systèmes d'information</v>
+      </c>
+      <c r="D4" t="str">
+        <v>En préparation</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>S15</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Inventaire du mobilier</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Planifié</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>S16</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Comité qualité trimestriel</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Direction générale</v>
+      </c>
+      <c r="D6" t="str">
+        <v>À confirmer</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>S17</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Mise à jour du guide d'accueil</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Communication</v>
+      </c>
+      <c r="D7" t="str">
         <v>Planifié</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Salle</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Capacité</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Équipement</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Salle A</v>
+      </c>
+      <c r="B2">
+        <v>20</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Vidéoprojecteur</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Salle B</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Écran interactif</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Auditorium</v>
+      </c>
+      <c r="B4">
+        <v>80</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Sonorisation</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>